--- a/M2.xlsx
+++ b/M2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8269B50-4A89-46EC-A538-8A237F880AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F81912-32E6-4BE8-9C40-DAE1B0FB7692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33930" yWindow="2625" windowWidth="21075" windowHeight="12945" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="M2 2025-2027" sheetId="10" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="65">
   <si>
     <t>päivä</t>
   </si>
@@ -218,6 +218,21 @@
   </si>
   <si>
     <t>2026-2027</t>
+  </si>
+  <si>
+    <t>20-25,23-25-16-25</t>
+  </si>
+  <si>
+    <t>3.10.2026</t>
+  </si>
+  <si>
+    <t>AitRi</t>
+  </si>
+  <si>
+    <t>27.9.2026</t>
+  </si>
+  <si>
+    <t>16-25,14-25,29-27,19-25</t>
   </si>
 </sst>
 </file>
@@ -763,7 +778,7 @@
       </c>
       <c r="C3" s="24">
         <f>'M2 2026-2027'!R2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="24">
         <f>'M2 2026-2027'!S2</f>
@@ -802,7 +817,7 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
@@ -899,19 +914,37 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="20"/>
+    <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>64</v>
+      </c>
       <c r="G2" s="20"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+      <c r="J2" s="10">
+        <v>1</v>
+      </c>
+      <c r="K2" s="10">
+        <v>78</v>
+      </c>
+      <c r="L2" s="10">
+        <v>102</v>
+      </c>
       <c r="M2" s="10"/>
       <c r="N2" s="11" t="s">
         <v>8</v>
@@ -923,26 +956,44 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
         <f>SUM(J2:J25)+SUM(I2:I25)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>60</v>
+      </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="J3" s="8">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8">
+        <v>59</v>
+      </c>
+      <c r="L3" s="8">
+        <v>75</v>
+      </c>
       <c r="M3" s="8"/>
       <c r="N3" s="7" t="s">
         <v>4</v>
@@ -954,11 +1005,11 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
         <f>SUM(J2:J25)*3+SUM(I2:I25)*2+SUM(H2:H25)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -980,16 +1031,16 @@
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K30)</f>
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L30)</f>
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>0</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">

--- a/M2.xlsx
+++ b/M2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F81912-32E6-4BE8-9C40-DAE1B0FB7692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3580AE-0712-4AC3-8E2D-E8C5B9B80550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="68">
   <si>
     <t>päivä</t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t>16-25,14-25,29-27,19-25</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>11.10.2026</t>
+  </si>
+  <si>
+    <t>9-25,17-25,22-25</t>
   </si>
 </sst>
 </file>
@@ -778,7 +787,7 @@
       </c>
       <c r="C3" s="24">
         <f>'M2 2026-2027'!R2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="24">
         <f>'M2 2026-2027'!S2</f>
@@ -817,7 +826,7 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
@@ -956,11 +965,11 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
         <f>SUM(J2:J25)+SUM(I2:I25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1005,47 +1014,65 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
         <f>SUM(J2:J25)*3+SUM(I2:I25)*2+SUM(H2:H25)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="20"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>67</v>
+      </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10">
+        <v>48</v>
+      </c>
+      <c r="L4" s="10">
+        <v>75</v>
+      </c>
       <c r="M4" s="10"/>
       <c r="N4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K30)</f>
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L30)</f>
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>314</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
@@ -1065,7 +1092,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="19"/>
-      <c r="B6" s="20"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
       <c r="E6" s="21"/>
@@ -1085,7 +1112,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
@@ -1105,7 +1132,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
-      <c r="B8" s="20"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
       <c r="E8" s="21"/>
@@ -1125,7 +1152,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
@@ -1145,7 +1172,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
-      <c r="B10" s="20"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
@@ -1165,7 +1192,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="15"/>
@@ -1185,7 +1212,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="21"/>
@@ -1205,7 +1232,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="17"/>
@@ -1225,7 +1252,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="21"/>
@@ -1245,7 +1272,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
-      <c r="B15" s="14"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
@@ -1265,7 +1292,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
       <c r="E16" s="21"/>
@@ -1285,7 +1312,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="15"/>
@@ -1305,7 +1332,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
       <c r="E18" s="21"/>
@@ -1325,7 +1352,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="18"/>
-      <c r="B19" s="14"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
@@ -1336,6 +1363,940 @@
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="19"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35338555-4C3B-4F48-AD20-7BBDECE7FD0C}">
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="18" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="9">
+        <v>3</v>
+      </c>
+      <c r="H1" s="9">
+        <v>2</v>
+      </c>
+      <c r="I1" s="9">
+        <v>1</v>
+      </c>
+      <c r="J1" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="19">
+        <v>45949</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10">
+        <v>1</v>
+      </c>
+      <c r="K2" s="10">
+        <v>70</v>
+      </c>
+      <c r="L2" s="10">
+        <v>97</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="10">
+        <f>SUM(G2:G25)+SUM(H2:H25)</f>
+        <v>5</v>
+      </c>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10">
+        <f>SUM(J2:J25)+SUM(I2:I25)</f>
+        <v>13</v>
+      </c>
+      <c r="R2" s="10">
+        <f>SUM(O2:Q2)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
+        <v>45956</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8">
+        <v>75</v>
+      </c>
+      <c r="L3" s="8">
+        <v>61</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="8">
+        <f>SUM(G2:G25)*3+SUM(H2:H25)*2+SUM(I2:I25)</f>
+        <v>16</v>
+      </c>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8">
+        <f>SUM(J2:J25)*3+SUM(I2:I25)*2+SUM(H2:H25)</f>
+        <v>38</v>
+      </c>
+      <c r="R3" s="8">
+        <f>SUM(O3:Q3)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>45963</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10">
+        <v>89</v>
+      </c>
+      <c r="L4" s="10">
+        <v>102</v>
+      </c>
+      <c r="M4" s="10"/>
+      <c r="N4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="10">
+        <f>SUM(K2:K30)</f>
+        <v>1414</v>
+      </c>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10">
+        <f>SUM(L2:L30)</f>
+        <v>1595</v>
+      </c>
+      <c r="R4" s="10">
+        <f>SUM(O4:Q4)</f>
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>45969</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="16"/>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8">
+        <v>111</v>
+      </c>
+      <c r="L5" s="8">
+        <v>109</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+    </row>
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>45976</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10">
+        <v>53</v>
+      </c>
+      <c r="L6" s="10">
+        <v>75</v>
+      </c>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+    </row>
+    <row r="7" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>45991</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8">
+        <v>98</v>
+      </c>
+      <c r="L7" s="8">
+        <v>82</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>45998</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10">
+        <v>61</v>
+      </c>
+      <c r="L8" s="10">
+        <v>77</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+    </row>
+    <row r="9" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46005</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8">
+        <v>105</v>
+      </c>
+      <c r="L9" s="8">
+        <v>102</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>46032</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="22">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
+        <v>88</v>
+      </c>
+      <c r="L10" s="10">
+        <v>94</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46040</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8">
+        <v>96</v>
+      </c>
+      <c r="L11" s="8">
+        <v>103</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>46047</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10">
+        <v>94</v>
+      </c>
+      <c r="L12" s="10">
+        <v>105</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46054</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>79</v>
+      </c>
+      <c r="L13" s="8">
+        <v>100</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>46061</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10">
+        <v>1</v>
+      </c>
+      <c r="K14" s="10">
+        <v>85</v>
+      </c>
+      <c r="L14" s="10">
+        <v>92</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+    </row>
+    <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>46068</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8">
+        <v>50</v>
+      </c>
+      <c r="L15" s="8">
+        <v>75</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>46075</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10">
+        <v>47</v>
+      </c>
+      <c r="L16" s="10">
+        <v>75</v>
+      </c>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+    </row>
+    <row r="17" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>46081</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8">
+        <v>110</v>
+      </c>
+      <c r="L17" s="8">
+        <v>96</v>
+      </c>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>46089</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="22"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10">
+        <v>50</v>
+      </c>
+      <c r="L18" s="10">
+        <v>75</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+    </row>
+    <row r="19" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <v>45731</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <v>53</v>
+      </c>
+      <c r="L19" s="8">
+        <v>75</v>
+      </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
@@ -1499,938 +2460,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35338555-4C3B-4F48-AD20-7BBDECE7FD0C}">
-  <dimension ref="A1:S29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="3" width="10.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="18" width="10.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="9">
-        <v>3</v>
-      </c>
-      <c r="H1" s="9">
-        <v>2</v>
-      </c>
-      <c r="I1" s="9">
-        <v>1</v>
-      </c>
-      <c r="J1" s="9">
-        <v>0</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
-        <v>45949</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10">
-        <v>1</v>
-      </c>
-      <c r="K2" s="10">
-        <v>70</v>
-      </c>
-      <c r="L2" s="10">
-        <v>97</v>
-      </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="10">
-        <f>SUM(G2:G25)+SUM(H2:H25)</f>
-        <v>5</v>
-      </c>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10">
-        <f>SUM(J2:J25)+SUM(I2:I25)</f>
-        <v>13</v>
-      </c>
-      <c r="R2" s="10">
-        <f>SUM(O2:Q2)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
-        <v>45956</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1</v>
-      </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8">
-        <v>75</v>
-      </c>
-      <c r="L3" s="8">
-        <v>61</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" s="8">
-        <f>SUM(G2:G25)*3+SUM(H2:H25)*2+SUM(I2:I25)</f>
-        <v>16</v>
-      </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8">
-        <f>SUM(J2:J25)*3+SUM(I2:I25)*2+SUM(H2:H25)</f>
-        <v>38</v>
-      </c>
-      <c r="R3" s="8">
-        <f>SUM(O3:Q3)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
-        <v>45963</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10">
-        <v>1</v>
-      </c>
-      <c r="K4" s="10">
-        <v>89</v>
-      </c>
-      <c r="L4" s="10">
-        <v>102</v>
-      </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="10">
-        <f>SUM(K2:K30)</f>
-        <v>1414</v>
-      </c>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10">
-        <f>SUM(L2:L30)</f>
-        <v>1595</v>
-      </c>
-      <c r="R4" s="10">
-        <f>SUM(O4:Q4)</f>
-        <v>3009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
-        <v>45969</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="8">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8">
-        <v>111</v>
-      </c>
-      <c r="L5" s="8">
-        <v>109</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-    </row>
-    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
-        <v>45976</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>53</v>
-      </c>
-      <c r="L6" s="10">
-        <v>75</v>
-      </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-    </row>
-    <row r="7" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>45991</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="16">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8">
-        <v>98</v>
-      </c>
-      <c r="L7" s="8">
-        <v>82</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-    </row>
-    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
-        <v>45998</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10">
-        <v>1</v>
-      </c>
-      <c r="K8" s="10">
-        <v>61</v>
-      </c>
-      <c r="L8" s="10">
-        <v>77</v>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-    </row>
-    <row r="9" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>46005</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8">
-        <v>105</v>
-      </c>
-      <c r="L9" s="8">
-        <v>102</v>
-      </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="19">
-        <v>46032</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="22">
-        <v>1</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10">
-        <v>88</v>
-      </c>
-      <c r="L10" s="10">
-        <v>94</v>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-    </row>
-    <row r="11" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>46040</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8">
-        <v>96</v>
-      </c>
-      <c r="L11" s="8">
-        <v>103</v>
-      </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-    </row>
-    <row r="12" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="19">
-        <v>46047</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10">
-        <v>1</v>
-      </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10">
-        <v>94</v>
-      </c>
-      <c r="L12" s="10">
-        <v>105</v>
-      </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-    </row>
-    <row r="13" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>46054</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8">
-        <v>1</v>
-      </c>
-      <c r="K13" s="8">
-        <v>79</v>
-      </c>
-      <c r="L13" s="8">
-        <v>100</v>
-      </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-    </row>
-    <row r="14" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="19">
-        <v>46061</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10">
-        <v>1</v>
-      </c>
-      <c r="K14" s="10">
-        <v>85</v>
-      </c>
-      <c r="L14" s="10">
-        <v>92</v>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-    </row>
-    <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
-        <v>46068</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8">
-        <v>1</v>
-      </c>
-      <c r="K15" s="8">
-        <v>50</v>
-      </c>
-      <c r="L15" s="8">
-        <v>75</v>
-      </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-    </row>
-    <row r="16" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="19">
-        <v>46075</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10">
-        <v>1</v>
-      </c>
-      <c r="K16" s="10">
-        <v>47</v>
-      </c>
-      <c r="L16" s="10">
-        <v>75</v>
-      </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-    </row>
-    <row r="17" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
-        <v>46081</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8">
-        <v>110</v>
-      </c>
-      <c r="L17" s="8">
-        <v>96</v>
-      </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-    </row>
-    <row r="18" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
-        <v>46089</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10">
-        <v>1</v>
-      </c>
-      <c r="K18" s="10">
-        <v>50</v>
-      </c>
-      <c r="L18" s="10">
-        <v>75</v>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-    </row>
-    <row r="19" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="18">
-        <v>45731</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8">
-        <v>53</v>
-      </c>
-      <c r="L19" s="8">
-        <v>75</v>
-      </c>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/M2.xlsx
+++ b/M2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3580AE-0712-4AC3-8E2D-E8C5B9B80550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E81120-9B3E-424D-8FC5-6247D234180A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="M2 2025-2027" sheetId="10" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
   <si>
     <t>päivä</t>
   </si>
@@ -133,9 +133,6 @@
     <t>JyLe</t>
   </si>
   <si>
-    <t>pisteet KaJe</t>
-  </si>
-  <si>
     <t>eräpisteet Kaje</t>
   </si>
   <si>
@@ -242,6 +239,15 @@
   </si>
   <si>
     <t>9-25,17-25,22-25</t>
+  </si>
+  <si>
+    <t>18.10.2026</t>
+  </si>
+  <si>
+    <t>18-25,25-18,17-25,20-25</t>
+  </si>
+  <si>
+    <t>pisteet omat</t>
   </si>
 </sst>
 </file>
@@ -725,13 +731,13 @@
         <v>16</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>18</v>
@@ -780,42 +786,41 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="C3" s="24">
         <f>'M2 2026-2027'!R2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="24">
-        <f>'M2 2026-2027'!S2</f>
+        <f>'M2 2026-2027'!O2</f>
         <v>0</v>
       </c>
       <c r="E3" s="24">
-        <f>'M2 2026-2027'!T2</f>
         <v>0</v>
       </c>
       <c r="F3" s="24">
-        <f>'M2 2026-2027'!U2</f>
+        <f>'M2 2026-2027'!Q2</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="24">
+        <f>'M2 2026-2027'!O3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="24">
-        <f>'M2 2026-2027'!V2</f>
-        <v>0</v>
-      </c>
       <c r="H3" s="24">
-        <f>'M2 2026-2027'!W2</f>
-        <v>0</v>
+        <f>'M2 2026-2027'!Q3</f>
+        <v>12</v>
       </c>
       <c r="I3" s="24">
-        <f>'M2 2026-2027'!X2</f>
-        <v>0</v>
+        <f>'M2 2026-2027'!O4</f>
+        <v>265</v>
       </c>
       <c r="J3" s="24">
-        <f>'M2 2026-2027'!Y2</f>
-        <v>0</v>
+        <f>'M2 2026-2027'!Q4</f>
+        <v>345</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -826,7 +831,7 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
@@ -838,7 +843,7 @@
       </c>
       <c r="F4" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" si="0"/>
@@ -846,15 +851,15 @@
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I4" s="12">
         <f t="shared" si="0"/>
-        <v>1414</v>
+        <v>1679</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>1595</v>
+        <v>1940</v>
       </c>
       <c r="K4" s="10"/>
     </row>
@@ -928,19 +933,19 @@
         <v>24</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="10"/>
@@ -965,11 +970,11 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
         <f>SUM(J2:J25)+SUM(I2:I25)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -977,19 +982,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -1014,11 +1019,11 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
         <f>SUM(J2:J25)*3+SUM(I2:I25)*2+SUM(H2:H25)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1026,19 +1031,19 @@
         <v>24</v>
       </c>
       <c r="B4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>66</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>67</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -1058,31 +1063,49 @@
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K30)</f>
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L30)</f>
-        <v>252</v>
+        <v>345</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>437</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="G5" s="16"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="J5" s="8">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>80</v>
+      </c>
+      <c r="L5" s="8">
+        <v>93</v>
+      </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -1702,7 +1725,7 @@
         <v>27</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -1748,10 +1771,10 @@
         <v>30</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>34</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>35</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="8">
@@ -1786,10 +1809,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>37</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="10"/>
@@ -1824,10 +1847,10 @@
         <v>23</v>
       </c>
       <c r="E7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="16" t="s">
         <v>38</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
       </c>
       <c r="G7" s="16">
         <v>1</v>
@@ -1865,7 +1888,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="10"/>
@@ -1900,10 +1923,10 @@
         <v>30</v>
       </c>
       <c r="E9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -1935,13 +1958,13 @@
         <v>21</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="22">
         <v>1</v>
@@ -1973,13 +1996,13 @@
         <v>21</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -2011,13 +2034,13 @@
         <v>21</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="22"/>
       <c r="H12" s="10"/>
@@ -2049,13 +2072,13 @@
         <v>21</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -2087,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="22"/>
       <c r="H14" s="10"/>
@@ -2125,13 +2148,13 @@
         <v>21</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -2163,13 +2186,13 @@
         <v>21</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="10"/>
@@ -2201,13 +2224,13 @@
         <v>21</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8">
@@ -2239,13 +2262,13 @@
         <v>21</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="10"/>
@@ -2277,13 +2300,13 @@
         <v>21</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>

--- a/M2.xlsx
+++ b/M2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E81120-9B3E-424D-8FC5-6247D234180A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460A2672-6732-48D5-BA1B-7826C039839C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="4152" yWindow="1068" windowWidth="17280" windowHeight="11580" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="M2 2025-2027" sheetId="10" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="73">
   <si>
     <t>päivä</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>pisteet omat</t>
+  </si>
+  <si>
+    <t>25.10.2026</t>
+  </si>
+  <si>
+    <t>Lempo</t>
+  </si>
+  <si>
+    <t>22-25,24-26,17-25</t>
   </si>
 </sst>
 </file>
@@ -793,7 +802,7 @@
       </c>
       <c r="C3" s="24">
         <f>'M2 2026-2027'!R2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="24">
         <f>'M2 2026-2027'!O2</f>
@@ -804,7 +813,7 @@
       </c>
       <c r="F3" s="24">
         <f>'M2 2026-2027'!Q2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="24">
         <f>'M2 2026-2027'!O3</f>
@@ -812,15 +821,15 @@
       </c>
       <c r="H3" s="24">
         <f>'M2 2026-2027'!Q3</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I3" s="24">
         <f>'M2 2026-2027'!O4</f>
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="J3" s="24">
         <f>'M2 2026-2027'!Q4</f>
-        <v>345</v>
+        <v>420</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -831,7 +840,7 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
@@ -843,7 +852,7 @@
       </c>
       <c r="F4" s="11">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" si="0"/>
@@ -851,15 +860,15 @@
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I4" s="12">
         <f t="shared" si="0"/>
-        <v>1679</v>
+        <v>1740</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>1940</v>
+        <v>2015</v>
       </c>
       <c r="K4" s="10"/>
     </row>
@@ -970,11 +979,11 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
         <f>SUM(J2:J25)+SUM(I2:I25)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1019,11 +1028,11 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
         <f>SUM(J2:J25)*3+SUM(I2:I25)*2+SUM(H2:H25)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1063,16 +1072,16 @@
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K30)</f>
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L30)</f>
-        <v>345</v>
+        <v>420</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>610</v>
+        <v>746</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -1113,19 +1122,37 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="22"/>
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10">
+        <v>61</v>
+      </c>
+      <c r="L6" s="10">
+        <v>75</v>
+      </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
